--- a/PACERISE_upload_template.xlsx
+++ b/PACERISE_upload_template.xlsx
@@ -400,19 +400,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L13"/>
+  <dimension ref="A1:M13"/>
   <cols>
-    <col min="1" max="1" width="16.83203125" customWidth="1"/>
-    <col min="2" max="2" width="10.83203125" customWidth="1"/>
-    <col min="3" max="3" width="6.83203125" customWidth="1"/>
-    <col min="4" max="4" width="12.83203125" customWidth="1"/>
-    <col min="5" max="5" width="12.83203125" customWidth="1"/>
-    <col min="6" max="6" width="12.83203125" customWidth="1"/>
-    <col min="7" max="7" width="10.83203125" customWidth="1"/>
-    <col min="8" max="8" width="10.83203125" customWidth="1"/>
-    <col min="9" max="9" width="14.83203125" customWidth="1"/>
-    <col min="10" max="10" width="10.83203125" customWidth="1"/>
-    <col min="11" max="11" width="10.83203125" customWidth="1"/>
     <col min="12" max="12" width="14.83203125" customWidth="1"/>
   </cols>
   <sheetData>
@@ -451,6 +440,9 @@
         <v>4x800mR</v>
       </c>
       <c r="L1" t="str">
+        <v>휴대폰</v>
+      </c>
+      <c r="M1" t="str">
         <v>바코드</v>
       </c>
     </row>
@@ -474,6 +466,9 @@
         <v>200m</v>
       </c>
       <c r="L2" t="str">
+        <v/>
+      </c>
+      <c r="M2" t="str">
         <v>BC10174</v>
       </c>
     </row>
@@ -500,6 +495,9 @@
         <v>O</v>
       </c>
       <c r="L3" t="str">
+        <v/>
+      </c>
+      <c r="M3" t="str">
         <v>BC10015</v>
       </c>
     </row>
@@ -529,6 +527,9 @@
         <v>O</v>
       </c>
       <c r="L4" t="str">
+        <v/>
+      </c>
+      <c r="M4" t="str">
         <v>BC10062</v>
       </c>
     </row>
@@ -552,6 +553,9 @@
         <v>3000mSC</v>
       </c>
       <c r="L5" t="str">
+        <v/>
+      </c>
+      <c r="M5" t="str">
         <v>BC10113</v>
       </c>
     </row>
@@ -572,6 +576,9 @@
         <v>5000m</v>
       </c>
       <c r="L6" t="str">
+        <v/>
+      </c>
+      <c r="M6" t="str">
         <v>BC10114</v>
       </c>
     </row>
@@ -598,6 +605,9 @@
         <v>O</v>
       </c>
       <c r="L7" t="str">
+        <v/>
+      </c>
+      <c r="M7" t="str">
         <v>BC10111</v>
       </c>
     </row>
@@ -624,6 +634,9 @@
         <v>O</v>
       </c>
       <c r="L8" t="str">
+        <v/>
+      </c>
+      <c r="M8" t="str">
         <v>BC10196</v>
       </c>
     </row>
@@ -653,6 +666,9 @@
         <v>O</v>
       </c>
       <c r="L9" t="str">
+        <v/>
+      </c>
+      <c r="M9" t="str">
         <v>BC10157</v>
       </c>
     </row>
@@ -676,6 +692,9 @@
         <v>1500m</v>
       </c>
       <c r="L10" t="str">
+        <v/>
+      </c>
+      <c r="M10" t="str">
         <v>BC10117</v>
       </c>
     </row>
@@ -702,6 +721,9 @@
         <v>O</v>
       </c>
       <c r="L11" t="str">
+        <v/>
+      </c>
+      <c r="M11" t="str">
         <v>BC10196F</v>
       </c>
     </row>
@@ -722,6 +744,9 @@
         <v>10종경기</v>
       </c>
       <c r="L12" t="str">
+        <v/>
+      </c>
+      <c r="M12" t="str">
         <v>BC10053</v>
       </c>
     </row>
@@ -742,12 +767,15 @@
         <v>10종경기</v>
       </c>
       <c r="L13" t="str">
+        <v/>
+      </c>
+      <c r="M13" t="str">
         <v>BC10088</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L13"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:M13"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -755,17 +783,6 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:I31"/>
-  <cols>
-    <col min="1" max="1" width="8.83203125" customWidth="1"/>
-    <col min="2" max="2" width="16.83203125" customWidth="1"/>
-    <col min="3" max="3" width="8.83203125" customWidth="1"/>
-    <col min="4" max="4" width="5.83203125" customWidth="1"/>
-    <col min="5" max="5" width="6.83203125" customWidth="1"/>
-    <col min="6" max="6" width="6.83203125" customWidth="1"/>
-    <col min="7" max="7" width="8.83203125" customWidth="1"/>
-    <col min="8" max="8" width="14.83203125" customWidth="1"/>
-    <col min="9" max="9" width="16.83203125" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1592,17 +1609,6 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:I10"/>
-  <cols>
-    <col min="1" max="1" width="8.83203125" customWidth="1"/>
-    <col min="2" max="2" width="16.83203125" customWidth="1"/>
-    <col min="3" max="3" width="8.83203125" customWidth="1"/>
-    <col min="4" max="4" width="5.83203125" customWidth="1"/>
-    <col min="5" max="5" width="6.83203125" customWidth="1"/>
-    <col min="6" max="6" width="6.83203125" customWidth="1"/>
-    <col min="7" max="7" width="8.83203125" customWidth="1"/>
-    <col min="8" max="8" width="14.83203125" customWidth="1"/>
-    <col min="9" max="9" width="16.83203125" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1876,9 +1882,9 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A53"/>
+  <dimension ref="A1:A60"/>
   <cols>
-    <col min="1" max="1" width="80.83203125" customWidth="1"/>
+    <col min="1" max="1" width="70.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2146,9 +2152,44 @@
         <v>- 조편성이 변경된 종목 + 기록 있음 → 경고 팝업 (선택)</v>
       </c>
     </row>
+    <row r="54">
+      <c r="A54" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="str">
+        <v>=== 휴대폰 / 문자(SMS) 관련 ===</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="str">
+        <v>• 선수명단 시트의 "휴대폰" 컬럼은 결과 안내 SMS 발송용입니다.</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="str">
+        <v>• 형식: 01012345678 (하이픈, 공백 자동 제거됨)</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="str">
+        <v>• 비워둬도 됩니다 — 비어 있는 선수는 SMS 발송 대상에서 자동 제외됩니다.</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="str">
+        <v>• 이후 관리자 페이지의 "선수 관리" 탭에서 개별 수정 가능합니다.</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="str">
+        <v>• 휴대폰만 업데이트하고 싶을 때는 "휴대폰 일괄 업로드" 기능을 사용하세요.</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:A53"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:A60"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/PACERISE_upload_template.xlsx
+++ b/PACERISE_upload_template.xlsx
@@ -402,7 +402,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M13"/>
   <cols>
-    <col min="12" max="12" width="14.83203125" customWidth="1"/>
+    <col min="5" max="5" width="14.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -419,28 +419,28 @@
         <v>생년월일</v>
       </c>
       <c r="E1" t="str">
+        <v>휴대폰</v>
+      </c>
+      <c r="F1" t="str">
         <v>종목1</v>
       </c>
-      <c r="F1" t="str">
+      <c r="G1" t="str">
         <v>종목2</v>
       </c>
-      <c r="G1" t="str">
+      <c r="H1" t="str">
         <v>4x100mR</v>
       </c>
-      <c r="H1" t="str">
+      <c r="I1" t="str">
         <v>4x400mR</v>
       </c>
-      <c r="I1" t="str">
+      <c r="J1" t="str">
         <v>Mixed 4x400mR</v>
       </c>
-      <c r="J1" t="str">
+      <c r="K1" t="str">
         <v>4x1500mR</v>
       </c>
-      <c r="K1" t="str">
+      <c r="L1" t="str">
         <v>4x800mR</v>
-      </c>
-      <c r="L1" t="str">
-        <v>휴대폰</v>
       </c>
       <c r="M1" t="str">
         <v>바코드</v>
@@ -460,13 +460,13 @@
         <v>2005-03-03</v>
       </c>
       <c r="E2" t="str">
+        <v/>
+      </c>
+      <c r="F2" t="str">
         <v>100m</v>
       </c>
-      <c r="F2" t="str">
+      <c r="G2" t="str">
         <v>200m</v>
-      </c>
-      <c r="L2" t="str">
-        <v/>
       </c>
       <c r="M2" t="str">
         <v>BC10174</v>
@@ -486,16 +486,16 @@
         <v>1991-04-19</v>
       </c>
       <c r="E3" t="str">
+        <v/>
+      </c>
+      <c r="F3" t="str">
         <v>100m</v>
       </c>
-      <c r="F3" t="str">
+      <c r="G3" t="str">
         <v>200m</v>
       </c>
-      <c r="G3" t="str">
+      <c r="H3" t="str">
         <v>O</v>
-      </c>
-      <c r="L3" t="str">
-        <v/>
       </c>
       <c r="M3" t="str">
         <v>BC10015</v>
@@ -515,19 +515,19 @@
         <v>2001-11-13</v>
       </c>
       <c r="E4" t="str">
+        <v/>
+      </c>
+      <c r="F4" t="str">
         <v>100m</v>
       </c>
-      <c r="F4" t="str">
+      <c r="G4" t="str">
         <v>200m</v>
-      </c>
-      <c r="G4" t="str">
-        <v>O</v>
       </c>
       <c r="H4" t="str">
         <v>O</v>
       </c>
-      <c r="L4" t="str">
-        <v/>
+      <c r="I4" t="str">
+        <v>O</v>
       </c>
       <c r="M4" t="str">
         <v>BC10062</v>
@@ -547,13 +547,13 @@
         <v>2000-05-12</v>
       </c>
       <c r="E5" t="str">
+        <v/>
+      </c>
+      <c r="F5" t="str">
         <v>5000m</v>
       </c>
-      <c r="F5" t="str">
+      <c r="G5" t="str">
         <v>3000mSC</v>
-      </c>
-      <c r="L5" t="str">
-        <v/>
       </c>
       <c r="M5" t="str">
         <v>BC10113</v>
@@ -573,10 +573,10 @@
         <v>1999-07-15</v>
       </c>
       <c r="E6" t="str">
+        <v/>
+      </c>
+      <c r="F6" t="str">
         <v>5000m</v>
-      </c>
-      <c r="L6" t="str">
-        <v/>
       </c>
       <c r="M6" t="str">
         <v>BC10114</v>
@@ -596,16 +596,16 @@
         <v>2001-03-22</v>
       </c>
       <c r="E7" t="str">
+        <v/>
+      </c>
+      <c r="F7" t="str">
         <v>5000m</v>
       </c>
-      <c r="F7" t="str">
+      <c r="G7" t="str">
         <v>10000m</v>
       </c>
-      <c r="K7" t="str">
+      <c r="L7" t="str">
         <v>O</v>
-      </c>
-      <c r="L7" t="str">
-        <v/>
       </c>
       <c r="M7" t="str">
         <v>BC10111</v>
@@ -625,16 +625,16 @@
         <v>1999-04-26</v>
       </c>
       <c r="E8" t="str">
+        <v/>
+      </c>
+      <c r="F8" t="str">
         <v>100m</v>
       </c>
-      <c r="F8" t="str">
+      <c r="G8" t="str">
         <v>200m</v>
       </c>
-      <c r="G8" t="str">
+      <c r="H8" t="str">
         <v>O</v>
-      </c>
-      <c r="L8" t="str">
-        <v/>
       </c>
       <c r="M8" t="str">
         <v>BC10196</v>
@@ -654,19 +654,19 @@
         <v>2004-01-15</v>
       </c>
       <c r="E9" t="str">
+        <v/>
+      </c>
+      <c r="F9" t="str">
         <v>100m</v>
       </c>
-      <c r="F9" t="str">
+      <c r="G9" t="str">
         <v>200m</v>
-      </c>
-      <c r="G9" t="str">
-        <v>O</v>
       </c>
       <c r="H9" t="str">
         <v>O</v>
       </c>
-      <c r="L9" t="str">
-        <v/>
+      <c r="I9" t="str">
+        <v>O</v>
       </c>
       <c r="M9" t="str">
         <v>BC10157</v>
@@ -686,13 +686,13 @@
         <v>2003-08-14</v>
       </c>
       <c r="E10" t="str">
+        <v/>
+      </c>
+      <c r="F10" t="str">
         <v>5000m</v>
       </c>
-      <c r="F10" t="str">
+      <c r="G10" t="str">
         <v>1500m</v>
-      </c>
-      <c r="L10" t="str">
-        <v/>
       </c>
       <c r="M10" t="str">
         <v>BC10117</v>
@@ -712,16 +712,16 @@
         <v>1995-02-28</v>
       </c>
       <c r="E11" t="str">
+        <v/>
+      </c>
+      <c r="F11" t="str">
         <v>100m</v>
-      </c>
-      <c r="G11" t="str">
-        <v>O</v>
       </c>
       <c r="H11" t="str">
         <v>O</v>
       </c>
-      <c r="L11" t="str">
-        <v/>
+      <c r="I11" t="str">
+        <v>O</v>
       </c>
       <c r="M11" t="str">
         <v>BC10196F</v>
@@ -741,10 +741,10 @@
         <v>1998-06-10</v>
       </c>
       <c r="E12" t="str">
+        <v/>
+      </c>
+      <c r="F12" t="str">
         <v>10종경기</v>
-      </c>
-      <c r="L12" t="str">
-        <v/>
       </c>
       <c r="M12" t="str">
         <v>BC10053</v>
@@ -764,10 +764,10 @@
         <v>2000-03-25</v>
       </c>
       <c r="E13" t="str">
+        <v/>
+      </c>
+      <c r="F13" t="str">
         <v>10종경기</v>
-      </c>
-      <c r="L13" t="str">
-        <v/>
       </c>
       <c r="M13" t="str">
         <v>BC10088</v>
@@ -1883,9 +1883,6 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:A60"/>
-  <cols>
-    <col min="1" max="1" width="70.83203125" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
